--- a/output/DANHSACHPHANCONG_ca2.XLSX
+++ b/output/DANHSACHPHANCONG_ca2.XLSX
@@ -11,6 +11,11 @@
     <sheet name="Phân công 3" r:id="rId5" sheetId="3"/>
     <sheet name="Phân công 4" r:id="rId6" sheetId="4"/>
     <sheet name="Phân công 5" r:id="rId7" sheetId="5"/>
+    <sheet name="Phân công 6" r:id="rId8" sheetId="6"/>
+    <sheet name="Phân công 7" r:id="rId9" sheetId="7"/>
+    <sheet name="Phân công 8" r:id="rId10" sheetId="8"/>
+    <sheet name="Phân công 9" r:id="rId11" sheetId="9"/>
+    <sheet name="Phân công 10" r:id="rId12" sheetId="10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Phân công 1'!$1:$4</definedName>
@@ -18,6 +23,11 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Phân công 3'!$1:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Phân công 4'!$1:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Phân công 5'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Phân công 6'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Phân công 7'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'Phân công 8'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'Phân công 9'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'Phân công 10'!$1:$4</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -166,12 +176,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>105150103</t>
+          <t>101170116</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Võ Năm</t>
+          <t>Phạm Hồng Lâm</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -186,7 +196,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>216</t>
         </is>
       </c>
     </row>
@@ -196,12 +206,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>101170001</t>
+          <t>101170128</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Nguyễn Văn An</t>
+          <t>Đặng Quang Phiên</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -216,7 +226,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>216</t>
         </is>
       </c>
     </row>
@@ -226,12 +236,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>101170002</t>
+          <t>101170117</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Lê Văn Anh</t>
+          <t>Lê Duy Linh</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -246,7 +256,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>166</t>
         </is>
       </c>
     </row>
@@ -256,12 +266,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>101170003</t>
+          <t>101170096</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Phan Hữu Bình</t>
+          <t>Nguyễn Đình Anh Dũng</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -276,7 +286,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>166</t>
         </is>
       </c>
     </row>
@@ -286,12 +296,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>101170004</t>
+          <t>101170196</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Đặng Vĩnh Chiến</t>
+          <t>Huỳnh Minh Nghĩa</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -306,7 +316,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>178</t>
         </is>
       </c>
     </row>
@@ -316,12 +326,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>101170005</t>
+          <t>101170065</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Đoàn Ngọc Chung</t>
+          <t>Bùi Thế Thiên</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -336,7 +346,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>178</t>
         </is>
       </c>
     </row>
@@ -346,12 +356,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>101170006</t>
+          <t>101170119</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Nguyễn Đình Chung</t>
+          <t>Bùi Tiến Lợi</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -366,7 +376,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>193</t>
         </is>
       </c>
     </row>
@@ -376,12 +386,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>101170007</t>
+          <t>101170186</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Đoàn Minh Văn Chương</t>
+          <t>Nguyễn Bá Khải</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -396,7 +406,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>193</t>
         </is>
       </c>
     </row>
@@ -406,12 +416,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>101170008</t>
+          <t>101170146</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Phan Văn Công</t>
+          <t>Phạm Văn Thắng</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -426,7 +436,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>200</t>
         </is>
       </c>
     </row>
@@ -436,12 +446,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>101170009</t>
+          <t>101170048</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Trần Danh Đán</t>
+          <t>Lê Hồng Phúc</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -456,7 +466,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>200</t>
         </is>
       </c>
     </row>
@@ -466,12 +476,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>101170010</t>
+          <t>101170141</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Nguyễn Hải Đạt</t>
+          <t>Trần Thanh Tâm</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -486,7 +496,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>147</t>
         </is>
       </c>
     </row>
@@ -496,12 +506,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>101170011</t>
+          <t>101170107</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Nguyễn Tiến Đạt</t>
+          <t>Nguyễn Đức Hoàng</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -516,7 +526,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>147</t>
         </is>
       </c>
     </row>
@@ -526,12 +536,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>101170012</t>
+          <t>101170153</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Nguyễn Cửu Thanh Đề</t>
+          <t>Lê Thạc Thùy</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -546,7 +556,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>163</t>
         </is>
       </c>
     </row>
@@ -556,12 +566,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>101170013</t>
+          <t>101170177</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Đặng Trọng Đức</t>
+          <t>Đặng Minh Hiếu</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -576,7 +586,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>163</t>
         </is>
       </c>
     </row>
@@ -586,12 +596,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>101170014</t>
+          <t>101170012</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Trần Hưng Đức</t>
+          <t>Nguyễn Cửu Thanh Đề</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -606,7 +616,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>168</t>
         </is>
       </c>
     </row>
@@ -616,12 +626,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>101170015</t>
+          <t>101170083</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Lê Minh Dũng</t>
+          <t>Trần Cao Dy Bảo</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -636,7 +646,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>168</t>
         </is>
       </c>
     </row>
@@ -646,12 +656,12 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>101170016</t>
+          <t>101170115</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Nguyễn Quốc Dũng</t>
+          <t>Vũ Trung Kiên</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -666,7 +676,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>137</t>
         </is>
       </c>
     </row>
@@ -676,12 +686,12 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>101170017</t>
+          <t>101170036</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Nguyễn Hữu Tùng Dương</t>
+          <t>Nguyễn Phan Thành Lộc</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -696,7 +706,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>137</t>
         </is>
       </c>
     </row>
@@ -706,12 +716,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>101170018</t>
+          <t>101170122</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Đặng Ngọc Giang</t>
+          <t>Võ Hoài Nam</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -726,7 +736,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>170</t>
         </is>
       </c>
     </row>
@@ -736,12 +746,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>101170019</t>
+          <t>101170041</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Đặng Hà</t>
+          <t>Nguyễn Lương Nghĩa</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -756,7 +766,441 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>170</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+  </mergeCells>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup usePrinterDefaults="false" orientation="portrait" fitToWidth="1" fitToHeight="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="true" fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="18.0" customWidth="true"/>
+    <col min="2" max="2" width="18.0" customWidth="true"/>
+    <col min="3" max="3" width="18.0" customWidth="true"/>
+    <col min="4" max="4" width="18.0" customWidth="true"/>
+    <col min="5" max="5" width="18.0" customWidth="true"/>
+    <col min="6" max="6" width="18.0" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Cộng Hòa Xã Hội Chủ Nghĩa Việt Nam</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Độc Lập - Tự Do - Hạnh Phúc</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+</row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>STT</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Mã GV</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Họ tên</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>Giám thị 1</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>Giám thị 2</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>Phòng thi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>181.0</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>101170054</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Trần Đắc Sáng</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>182.0</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>101170129</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Trần Hoàng Phong</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>183.0</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>101170002</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Lê Văn Anh</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>184.0</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>101170178</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Vũ Minh Hiếu</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>185.0</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>101170121</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Tôn Thất Minh</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>186.0</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>101170149</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Hà Đức Thiện</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>187.0</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>105150103</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Võ Năm</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>188.0</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>101170165</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Cao Đình Ái</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>189.0</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>101170093</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Nguyễn Tuấn Điệp</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>190.0</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>111160014</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Võ Đình Cường</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>191.0</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>101170037</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Phạm Đức Mạnh</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>192.0</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>101170131</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Hoàng Khắc Phúc</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>207</t>
         </is>
       </c>
     </row>
@@ -840,12 +1284,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>101170020</t>
+          <t>101170143</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Nguyễn Thanh Hải</t>
+          <t>Lê Phạm Quang Thái</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -860,7 +1304,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>174</t>
         </is>
       </c>
     </row>
@@ -870,12 +1314,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>101170021</t>
+          <t>101170173</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Trần Vĩnh Hảo</t>
+          <t>Cao Văn Đông</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -890,7 +1334,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>174</t>
         </is>
       </c>
     </row>
@@ -900,12 +1344,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>101170022</t>
+          <t>101170201</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Đặng Văn Hiếu</t>
+          <t>Trần Duy Phương</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -920,7 +1364,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>146</t>
         </is>
       </c>
     </row>
@@ -930,12 +1374,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>101170023</t>
+          <t>101170066</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Nguyễn Trung Hiếu</t>
+          <t>Nguyễn Công Thiện</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -950,7 +1394,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>146</t>
         </is>
       </c>
     </row>
@@ -960,12 +1404,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>101170024</t>
+          <t>101170038</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Võ Đăng Hiếu</t>
+          <t>Nguyễn Văn Minh</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -980,7 +1424,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>181</t>
         </is>
       </c>
     </row>
@@ -990,12 +1434,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>101170025</t>
+          <t>101170008</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Trần Văn Hòa</t>
+          <t>Phan Văn Công</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1010,7 +1454,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>181</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1464,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>101170026</t>
+          <t>101170063</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Nguyễn Đình Hoàng</t>
+          <t>Phan Dũng Thắng</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1040,7 +1484,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>206</t>
         </is>
       </c>
     </row>
@@ -1050,12 +1494,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>101170027</t>
+          <t>101170124</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Nguyễn Minh Hoàng</t>
+          <t>Đinh Văn Nguyên</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1070,7 +1514,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>206</t>
         </is>
       </c>
     </row>
@@ -1080,12 +1524,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>101170028</t>
+          <t>101170052</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Nguyễn Mạnh Hùng</t>
+          <t>Đỗ Văn Quang</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1100,7 +1544,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>195</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1554,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>101170029</t>
+          <t>101170094</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Trương Văn Hùng</t>
+          <t>Đậu Thế Đức</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1130,7 +1574,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>195</t>
         </is>
       </c>
     </row>
@@ -1140,12 +1584,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>101170030</t>
+          <t>101170005</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Lê Đức Huy</t>
+          <t>Đoàn Ngọc Chung</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1160,7 +1604,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>190</t>
         </is>
       </c>
     </row>
@@ -1170,12 +1614,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>101170031</t>
+          <t>101170056</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Trần Văn Huy</t>
+          <t>Đoàn Nguyên Anh Tài</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1190,7 +1634,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>190</t>
         </is>
       </c>
     </row>
@@ -1200,12 +1644,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>101170032</t>
+          <t>101170118</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Lê Trung Kiên</t>
+          <t>Võ Duy Linh</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1220,7 +1664,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>188</t>
         </is>
       </c>
     </row>
@@ -1230,12 +1674,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>101170033</t>
+          <t>101170188</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Hoàng Phan Lâm</t>
+          <t>Trần Thành Khoa</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1250,7 +1694,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>188</t>
         </is>
       </c>
     </row>
@@ -1260,12 +1704,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>101170034</t>
+          <t>101170091</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Trần Hoàng Lâm</t>
+          <t>Nguyễn Phi Đạt</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1280,7 +1724,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>212</t>
         </is>
       </c>
     </row>
@@ -1290,12 +1734,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>101170035</t>
+          <t>101170013</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Trần Quang Linh</t>
+          <t>Đặng Trọng Đức</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1310,7 +1754,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>212</t>
         </is>
       </c>
     </row>
@@ -1320,12 +1764,12 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>101170036</t>
+          <t>101170010</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Nguyễn Phan Thành Lộc</t>
+          <t>Nguyễn Hải Đạt</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1340,7 +1784,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>138</t>
         </is>
       </c>
     </row>
@@ -1350,12 +1794,12 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>101170037</t>
+          <t>101170084</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Phạm Đức Mạnh</t>
+          <t>Võ Thành Châu</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1370,7 +1814,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>138</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1824,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>101170038</t>
+          <t>101170103</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Minh</t>
+          <t>Lê Minh Hiếu</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1400,7 +1844,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>129</t>
         </is>
       </c>
     </row>
@@ -1410,12 +1854,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>101170039</t>
+          <t>101170109</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Văn Nhật Nam</t>
+          <t>Phan Mạnh Hùng</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1430,7 +1874,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>129</t>
         </is>
       </c>
     </row>
@@ -1514,12 +1958,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>101170040</t>
+          <t>101170169</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Lê Đình Ngà</t>
+          <t>Huỳnh Văn Chiến</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1534,7 +1978,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>128</t>
         </is>
       </c>
     </row>
@@ -1544,12 +1988,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>101170041</t>
+          <t>101170039</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Nguyễn Lương Nghĩa</t>
+          <t>Văn Nhật Nam</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1564,7 +2008,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>128</t>
         </is>
       </c>
     </row>
@@ -1574,12 +2018,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>101170042</t>
+          <t>101170185</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Nguyện</t>
+          <t>Phan Minh Huy</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1594,7 +2038,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>210</t>
         </is>
       </c>
     </row>
@@ -1604,12 +2048,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>101170043</t>
+          <t>101170111</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Lê Nhật</t>
+          <t>Nguyễn Tài Huy</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1624,7 +2068,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>210</t>
         </is>
       </c>
     </row>
@@ -1634,12 +2078,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>101170044</t>
+          <t>101170197</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Nguyễn Huỳnh Nhật</t>
+          <t>Đoàn Chí Nhật</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1654,7 +2098,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>164</t>
         </is>
       </c>
     </row>
@@ -1664,12 +2108,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>101170045</t>
+          <t>101170110</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Lê Thị Nhựt</t>
+          <t>Phạm Nhật Hưng</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1684,7 +2128,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>164</t>
         </is>
       </c>
     </row>
@@ -1694,12 +2138,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>101170046</t>
+          <t>101170127</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Ngô Văn Phú</t>
+          <t>Nguyễn Minh Nhật</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1714,7 +2158,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>144</t>
         </is>
       </c>
     </row>
@@ -1724,12 +2168,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>101170047</t>
+          <t>101170080</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Hà Minh Phúc</t>
+          <t>Trần Hoàng Vũ</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1744,7 +2188,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>144</t>
         </is>
       </c>
     </row>
@@ -1754,12 +2198,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>101170048</t>
+          <t>101170006</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Lê Hồng Phúc</t>
+          <t>Nguyễn Đình Chung</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1774,7 +2218,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>139</t>
         </is>
       </c>
     </row>
@@ -1784,12 +2228,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>101170049</t>
+          <t>101170068</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Phan Văn Phúc</t>
+          <t>Phan Minh Thọ</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1804,7 +2248,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>139</t>
         </is>
       </c>
     </row>
@@ -1814,12 +2258,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>101170050</t>
+          <t>101170024</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Nguyễn Tăng Phước</t>
+          <t>Võ Đăng Hiếu</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1834,7 +2278,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>194</t>
         </is>
       </c>
     </row>
@@ -1844,12 +2288,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>101170051</t>
+          <t>101170156</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Nguyễn Đức Anh Quân</t>
+          <t>Nguyễn Hữu Trưởng</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1864,7 +2308,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>194</t>
         </is>
       </c>
     </row>
@@ -1874,12 +2318,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>101170052</t>
+          <t>101170003</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Đỗ Văn Quang</t>
+          <t>Phan Hữu Bình</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1894,7 +2338,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>149</t>
         </is>
       </c>
     </row>
@@ -1904,12 +2348,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>101170053</t>
+          <t>101170026</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Nguyễn Trần Văn Quốc</t>
+          <t>Nguyễn Đình Hoàng</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1924,7 +2368,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>149</t>
         </is>
       </c>
     </row>
@@ -1934,12 +2378,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>101170054</t>
+          <t>101170072</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Trần Đắc Sáng</t>
+          <t>Nguyễn Kế Trọng</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1954,7 +2398,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>172</t>
         </is>
       </c>
     </row>
@@ -1964,12 +2408,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>101170055</t>
+          <t>101170108</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Đỗ Hồng Sơn</t>
+          <t>Phan Thiên Hoàng</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1984,7 +2428,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>172</t>
         </is>
       </c>
     </row>
@@ -1994,12 +2438,12 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>101170056</t>
+          <t>101170135</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Đoàn Nguyên Anh Tài</t>
+          <t>Nguyễn Việt Quân</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -2014,7 +2458,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>196</t>
         </is>
       </c>
     </row>
@@ -2024,12 +2468,12 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>101170057</t>
+          <t>101170098</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Lê Bích Tâm</t>
+          <t>Võ Tấn Duy</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -2044,7 +2488,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>196</t>
         </is>
       </c>
     </row>
@@ -2054,12 +2498,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>101170058</t>
+          <t>101170022</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Đỗ Minh Tân</t>
+          <t>Đặng Văn Hiếu</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -2074,7 +2518,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>167</t>
         </is>
       </c>
     </row>
@@ -2084,12 +2528,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>101170059</t>
+          <t>101170069</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Nguyễn Quốc Tế</t>
+          <t>Huỳnh Văn Thu</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -2104,7 +2548,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>167</t>
         </is>
       </c>
     </row>
@@ -2188,12 +2632,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>101170060</t>
+          <t>101170138</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Nguyễn Lương Đức Hồng Thái</t>
+          <t>Nguyễn Duy Sáng</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -2208,7 +2652,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>145</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2662,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>101170061</t>
+          <t>101170001</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Hà Đình Thắng</t>
+          <t>Nguyễn Văn An</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2238,7 +2682,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>145</t>
         </is>
       </c>
     </row>
@@ -2248,12 +2692,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>101170062</t>
+          <t>101170142</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Ngô Xuân Thắng</t>
+          <t>Nguyễn Quang Tấn</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2268,7 +2712,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>218</t>
         </is>
       </c>
     </row>
@@ -2278,12 +2722,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>101170063</t>
+          <t>101170126</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Phan Dũng Thắng</t>
+          <t>Nguyễn Duy Nhật</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2298,7 +2742,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>218</t>
         </is>
       </c>
     </row>
@@ -2308,12 +2752,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>101170064</t>
+          <t>101170112</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Trần Ngọc Thành</t>
+          <t>Võ Quang Huy</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2328,7 +2772,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>222</t>
         </is>
       </c>
     </row>
@@ -2338,12 +2782,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>101170065</t>
+          <t>101170187</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Bùi Thế Thiên</t>
+          <t>Lê Ngọc Khánh</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -2358,7 +2802,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>222</t>
         </is>
       </c>
     </row>
@@ -2368,12 +2812,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>101170066</t>
+          <t>101170147</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Nguyễn Công Thiện</t>
+          <t>Lê Trung Thanh</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -2388,7 +2832,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>201</t>
         </is>
       </c>
     </row>
@@ -2398,12 +2842,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>101170067</t>
+          <t>101170076</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Huỳnh Văn Thịnh</t>
+          <t>Hoàng Nhật Tuyên</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2418,7 +2862,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>201</t>
         </is>
       </c>
     </row>
@@ -2428,12 +2872,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>101170068</t>
+          <t>101170174</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Phan Minh Thọ</t>
+          <t>Nguyễn Minh Đức</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -2448,7 +2892,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>199</t>
         </is>
       </c>
     </row>
@@ -2458,12 +2902,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>101170069</t>
+          <t>101170183</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Huỳnh Văn Thu</t>
+          <t>Lê Tự Huy</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -2478,7 +2922,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>199</t>
         </is>
       </c>
     </row>
@@ -2488,12 +2932,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>101170070</t>
+          <t>101170114</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Lê Tự Tiến</t>
+          <t>Nguyễn Trọng Khương</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2508,7 +2952,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>180</t>
         </is>
       </c>
     </row>
@@ -2518,12 +2962,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>101170071</t>
+          <t>101170180</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Phan Văn Tới</t>
+          <t>Trần Bá Hoàng</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2538,7 +2982,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>180</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2992,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>101170072</t>
+          <t>101170067</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Nguyễn Kế Trọng</t>
+          <t>Huỳnh Văn Thịnh</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -2568,7 +3012,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>155</t>
         </is>
       </c>
     </row>
@@ -2578,12 +3022,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>101170073</t>
+          <t>101170090</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Lê Anh Tú</t>
+          <t>Nguyễn Bảo Danh</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2598,7 +3042,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>155</t>
         </is>
       </c>
     </row>
@@ -2608,12 +3052,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>101170074</t>
+          <t>101170055</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Nguyễn Anh Tuấn</t>
+          <t>Đỗ Hồng Sơn</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -2628,7 +3072,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>179</t>
         </is>
       </c>
     </row>
@@ -2638,12 +3082,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>101170075</t>
+          <t>101170030</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Tuấn</t>
+          <t>Lê Đức Huy</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -2658,7 +3102,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>179</t>
         </is>
       </c>
     </row>
@@ -2668,12 +3112,12 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>101170076</t>
+          <t>101170190</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Hoàng Nhật Tuyên</t>
+          <t>Trần Đại Lâm</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -2688,7 +3132,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>162</t>
         </is>
       </c>
     </row>
@@ -2698,12 +3142,12 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>101170077</t>
+          <t>101170150</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Lê Phụ Vân</t>
+          <t>Trương Hoàng Thiện</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -2718,7 +3162,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>162</t>
         </is>
       </c>
     </row>
@@ -2728,12 +3172,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>101170078</t>
+          <t>101170058</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Lê Quốc Việt</t>
+          <t>Đỗ Minh Tân</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -2748,7 +3192,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>214</t>
         </is>
       </c>
     </row>
@@ -2758,12 +3202,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>101170079</t>
+          <t>101170198</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Lâm Quốc Vũ</t>
+          <t>Nguyễn Viết Như</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -2778,7 +3222,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>214</t>
         </is>
       </c>
     </row>
@@ -2862,12 +3306,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>101170080</t>
+          <t>101170203</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Trần Hoàng Vũ</t>
+          <t>Võ Đức Quãng</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -2882,7 +3326,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>141</t>
         </is>
       </c>
     </row>
@@ -2892,12 +3336,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>111160014</t>
+          <t>101170200</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Võ Đình Cường</t>
+          <t>Trịnh Hồng Phúc</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2912,7 +3356,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>141</t>
         </is>
       </c>
     </row>
@@ -2922,12 +3366,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>101170081</t>
+          <t>101170087</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Trần Viết An</t>
+          <t>Nguyễn Văn Chung</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2942,7 +3386,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>135</t>
         </is>
       </c>
     </row>
@@ -2952,12 +3396,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>101170082</t>
+          <t>101170194</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Lê Văn Bắc</t>
+          <t>Nghiêm Tuấn Minh</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2972,7 +3416,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>135</t>
         </is>
       </c>
     </row>
@@ -2982,12 +3426,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>101170083</t>
+          <t>101170136</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Trần Cao Dy Bảo</t>
+          <t>Võ Nhật Quang</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -3002,7 +3446,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>169</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3456,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>101170084</t>
+          <t>101170023</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Võ Thành Châu</t>
+          <t>Nguyễn Trung Hiếu</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3032,7 +3476,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>169</t>
         </is>
       </c>
     </row>
@@ -3042,12 +3486,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>101170085</t>
+          <t>101170014</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Trần Đình Chiến</t>
+          <t>Trần Hưng Đức</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3062,7 +3506,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>148</t>
         </is>
       </c>
     </row>
@@ -3072,12 +3516,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>101170086</t>
+          <t>101170148</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Lê Văn Chung</t>
+          <t>Nguyễn Đức Thảo</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3092,7 +3536,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>148</t>
         </is>
       </c>
     </row>
@@ -3102,12 +3546,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>101170087</t>
+          <t>101170007</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Chung</t>
+          <t>Đoàn Minh Văn Chương</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3122,7 +3566,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>197</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3576,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>101170088</t>
+          <t>101170057</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Nguyễn Đức Thành Công</t>
+          <t>Lê Bích Tâm</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -3152,7 +3596,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>197</t>
         </is>
       </c>
     </row>
@@ -3162,12 +3606,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>101170089</t>
+          <t>101170011</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Cường</t>
+          <t>Nguyễn Tiến Đạt</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -3182,7 +3626,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>186</t>
         </is>
       </c>
     </row>
@@ -3192,12 +3636,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>101170090</t>
+          <t>101170140</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Nguyễn Bảo Danh</t>
+          <t>Nguyễn Văn Sỹ</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -3212,7 +3656,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>186</t>
         </is>
       </c>
     </row>
@@ -3222,12 +3666,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>101170091</t>
+          <t>101170040</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Nguyễn Phi Đạt</t>
+          <t>Lê Đình Ngà</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -3242,7 +3686,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>198</t>
         </is>
       </c>
     </row>
@@ -3252,12 +3696,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>101170092</t>
+          <t>101170085</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Võ Xuân Đạt</t>
+          <t>Trần Đình Chiến</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -3272,7 +3716,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>198</t>
         </is>
       </c>
     </row>
@@ -3282,12 +3726,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>101170093</t>
+          <t>101170168</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Nguyễn Tuấn Điệp</t>
+          <t>Lê Hoàng Bửu</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -3302,7 +3746,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>205</t>
         </is>
       </c>
     </row>
@@ -3312,12 +3756,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>101170094</t>
+          <t>101170016</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Đậu Thế Đức</t>
+          <t>Nguyễn Quốc Dũng</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -3332,7 +3776,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>205</t>
         </is>
       </c>
     </row>
@@ -3342,12 +3786,12 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>101170095</t>
+          <t>101170059</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Võ Hữu Đức</t>
+          <t>Nguyễn Quốc Tế</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -3362,7 +3806,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>185</t>
         </is>
       </c>
     </row>
@@ -3372,12 +3816,12 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>101170096</t>
+          <t>101170044</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Nguyễn Đình Anh Dũng</t>
+          <t>Nguyễn Huỳnh Nhật</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -3392,7 +3836,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>185</t>
         </is>
       </c>
     </row>
@@ -3402,12 +3846,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>101170097</t>
+          <t>101170152</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Nguyễn Cảnh Dương</t>
+          <t>Trần Phong Thọ</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -3422,7 +3866,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>140</t>
         </is>
       </c>
     </row>
@@ -3432,12 +3876,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>101170098</t>
+          <t>101170075</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Võ Tấn Duy</t>
+          <t>Nguyễn Văn Tuấn</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3452,7 +3896,2703 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
+          <t>140</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+  </mergeCells>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup usePrinterDefaults="false" orientation="portrait" fitToWidth="1" fitToHeight="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="true" fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="18.0" customWidth="true"/>
+    <col min="2" max="2" width="18.0" customWidth="true"/>
+    <col min="3" max="3" width="18.0" customWidth="true"/>
+    <col min="4" max="4" width="18.0" customWidth="true"/>
+    <col min="5" max="5" width="18.0" customWidth="true"/>
+    <col min="6" max="6" width="18.0" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Cộng Hòa Xã Hội Chủ Nghĩa Việt Nam</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Độc Lập - Tự Do - Hạnh Phúc</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+</row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>STT</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Mã GV</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Họ tên</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>Giám thị 1</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>Giám thị 2</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>Phòng thi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>101.0</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>101170009</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Trần Danh Đán</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>102.0</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>101170132</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Nguyễn Văn Phúc</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>103.0</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>101170088</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Nguyễn Đức Thành Công</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>104.0</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>101170175</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Phạm Sự Đông Dương</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>105.0</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>101170120</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Trịnh Đình Mão</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>106.0</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>101170020</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Nguyễn Thanh Hải</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>107.0</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>101170172</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Hồ Minh Đạt</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>108.0</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>101170049</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Phan Văn Phúc</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>109.0</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>101170046</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Ngô Văn Phú</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>110.0</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>101170206</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Hoàng Đình Sao</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>111.0</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>101170035</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Trần Quang Linh</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>112.0</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>101170133</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Trần Hoàng Phúc</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>113.0</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>101170123</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Dương Bá Nghĩa</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>114.0</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>101170004</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Đặng Vĩnh Chiến</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>115.0</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>101170176</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Nguyễn Hưng Giao</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>177</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>116.0</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>101170155</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Nguyễn Nho Trịnh</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>117.0</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>101170015</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Lê Minh Dũng</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>118.0</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>101170079</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Lâm Quốc Vũ</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>119.0</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>101170193</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Nguyễn Luân</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>120.0</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>101170025</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Trần Văn Hòa</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+  </mergeCells>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup usePrinterDefaults="false" orientation="portrait" fitToWidth="1" fitToHeight="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="true" fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="18.0" customWidth="true"/>
+    <col min="2" max="2" width="18.0" customWidth="true"/>
+    <col min="3" max="3" width="18.0" customWidth="true"/>
+    <col min="4" max="4" width="18.0" customWidth="true"/>
+    <col min="5" max="5" width="18.0" customWidth="true"/>
+    <col min="6" max="6" width="18.0" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Cộng Hòa Xã Hội Chủ Nghĩa Việt Nam</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Độc Lập - Tự Do - Hạnh Phúc</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+</row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>STT</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Mã GV</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Họ tên</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>Giám thị 1</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>Giám thị 2</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>Phòng thi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>121.0</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>101170043</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Lê Nhật</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>122.0</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>101170018</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Đặng Ngọc Giang</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>123.0</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>101170050</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Nguyễn Tăng Phước</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>124.0</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>101170086</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Lê Văn Chung</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>125.0</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>101170151</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Nguyễn Quý Thịnh</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>126.0</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>101170029</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Trương Văn Hùng</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>127.0</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>101170082</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Lê Văn Bắc</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>128.0</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>101170045</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Lê Thị Nhựt</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>129.0</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>101170070</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Lê Tự Tiến</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>130.0</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>101170097</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Nguyễn Cảnh Dương</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>131.0</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>101170077</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Lê Phụ Vân</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>132.0</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>101170134</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Trần Đình Phương</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>133.0</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>101170074</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Nguyễn Anh Tuấn</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>134.0</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>101170171</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Nguyễn Văn Cường</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>135.0</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>101170089</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Nguyễn Văn Cường</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>136.0</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>101170179</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Ngô Hoàng</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>137.0</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>101170166</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Trần Tiến Anh</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>138.0</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>101170095</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Võ Hữu Đức</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>139.0</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>101170184</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Ngô Hoàng Huy</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>140.0</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>101170182</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Nguyễn Tấn Hưng</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+  </mergeCells>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup usePrinterDefaults="false" orientation="portrait" fitToWidth="1" fitToHeight="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="true" fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="18.0" customWidth="true"/>
+    <col min="2" max="2" width="18.0" customWidth="true"/>
+    <col min="3" max="3" width="18.0" customWidth="true"/>
+    <col min="4" max="4" width="18.0" customWidth="true"/>
+    <col min="5" max="5" width="18.0" customWidth="true"/>
+    <col min="6" max="6" width="18.0" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Cộng Hòa Xã Hội Chủ Nghĩa Việt Nam</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Độc Lập - Tự Do - Hạnh Phúc</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+</row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>STT</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Mã GV</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Họ tên</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>Giám thị 1</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>Giám thị 2</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>Phòng thi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>141.0</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>101170144</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>NguyễN Sỹ TháI</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>142.0</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>101170061</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Hà Đình Thắng</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>143.0</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>101170017</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Nguyễn Hữu Tùng Dương</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>144.0</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>101170019</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Đặng Hà</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>145.0</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>101170053</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Nguyễn Trần Văn Quốc</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>146.0</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>101170202</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Trần Văn Phượng</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>147.0</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>101170034</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Trần Hoàng Lâm</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>148.0</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>101170102</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Đặng Minh Hiếu</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>149.0</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>101170027</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Nguyễn Minh Hoàng</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>150.0</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>101170191</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Nguyễn Thanh Lộc</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>151.0</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>101170199</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Lê Minh Phong</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>152.0</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>101170154</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Nguyễn Trung Tín</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>153.0</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>101170021</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Trần Vĩnh Hảo</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>154.0</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>101170106</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Nguyễn Công Hoàng</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>155.0</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>101170130</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Trần Văn Phú</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>156.0</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>101170145</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Hoàng Phước Thắng</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>157.0</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>101170042</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Nguyễn Văn Nguyện</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>158.0</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>101170167</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Hồ Viết Bảo</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>159.0</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>101170181</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Nguyễn Văn Hùng</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>160.0</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>101170139</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Trần Văn Sĩ</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+  </mergeCells>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup usePrinterDefaults="false" orientation="portrait" fitToWidth="1" fitToHeight="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="true" fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="18.0" customWidth="true"/>
+    <col min="2" max="2" width="18.0" customWidth="true"/>
+    <col min="3" max="3" width="18.0" customWidth="true"/>
+    <col min="4" max="4" width="18.0" customWidth="true"/>
+    <col min="5" max="5" width="18.0" customWidth="true"/>
+    <col min="6" max="6" width="18.0" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Cộng Hòa Xã Hội Chủ Nghĩa Việt Nam</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Độc Lập - Tự Do - Hạnh Phúc</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+</row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>STT</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Mã GV</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Họ tên</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>Giám thị 1</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>Giám thị 2</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>Phòng thi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>161.0</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>101170099</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Nguyễn Hữu Giáp</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>162.0</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>101170081</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Trần Viết An</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>163.0</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>101170104</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Nguyễn Văn Hiếu</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>164.0</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>101170204</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Võ Văn Quý</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>165.0</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>101170195</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Trần Công Minh</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>166.0</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>101170064</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Trần Ngọc Thành</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>167.0</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>101170092</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Võ Xuân Đạt</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>168.0</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>101170137</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Nguyễn Văn Quyền</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>169.0</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>101170028</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Nguyễn Mạnh Hùng</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>170.0</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>101170060</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Nguyễn Lương Đức Hồng Thái</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>171.0</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>101170125</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Huỳnh Công Nhạc</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>172.0</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>101170105</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Võ Minh Hiếu</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>173.0</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>101170062</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Ngô Xuân Thắng</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>174.0</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>101170031</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Trần Văn Huy</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>175.0</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>101170071</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Phan Văn Tới</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>176.0</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>101170032</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Lê Trung Kiên</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>177.0</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>101170113</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Phan Hoài Khanh</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>178.0</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>101170100</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Đặng Ngọc Tính Hải</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>179.0</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>101170033</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Hoàng Phan Lâm</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>180.0</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>101170170</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Trương Văn Chương</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>133</t>
         </is>
       </c>
     </row>
